--- a/output/graficos_dimensiones/comunal_d_depmen_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:29</t>
+    <t xml:space="preserve">2026-08-17 16:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 16:16</t>
+    <t xml:space="preserve">2026-08-17 19:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 19:55</t>
+    <t xml:space="preserve">2026-09-01 17:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2018_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 17:31</t>
+    <t xml:space="preserve">2026-09-06 22:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
